--- a/data/trans_bre/IP16B01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,87</t>
+          <t>0,0; 10,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 24,3</t>
+          <t>-2,71; 23,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 32,24</t>
+          <t>-29,35; 29,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 32,98</t>
+          <t>-2,77; 31,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 56,48</t>
+          <t>-33,98; 49,97</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,77; -11,84</t>
+          <t>-43,06; -12,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 14,71</t>
+          <t>-11,58; 12,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,88; -12,48</t>
+          <t>-44,26; -13,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 17,85</t>
+          <t>-12,39; 14,55</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-38,71; -7,24</t>
+          <t>-38,99; -6,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,9; -0,62</t>
+          <t>-38,12; -0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,82; -7,82</t>
+          <t>-40,42; -6,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,67; -1,65</t>
+          <t>-39,22; -1,21</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 9,02</t>
+          <t>-20,39; 6,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 11,81</t>
+          <t>-30,87; 12,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 10,4</t>
+          <t>-21,46; 7,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 13,87</t>
+          <t>-34,06; 14,38</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -3,56</t>
+          <t>-18,93; -3,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 3,5</t>
+          <t>-16,11; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,3; -3,97</t>
+          <t>-20,29; -4,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 4,18</t>
+          <t>-17,81; 3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,93</t>
+          <t>0,0; 11,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 23,25</t>
+          <t>-2,91; 23,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 29,66</t>
+          <t>-25,36; 32,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 31,82</t>
+          <t>-2,93; 31,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 49,97</t>
+          <t>-28,31; 57,78</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,06; -12,21</t>
+          <t>-41,96; -11,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 12,39</t>
+          <t>-11,39; 13,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,26; -13,24</t>
+          <t>-43,08; -11,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 14,55</t>
+          <t>-11,65; 16,54</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-38,99; -6,44</t>
+          <t>-40,1; -6,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -0,98</t>
+          <t>-37,33; -1,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,42; -6,98</t>
+          <t>-41,28; -7,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,22; -1,21</t>
+          <t>-39,22; -2,26</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 6,92</t>
+          <t>-20,32; 7,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 12,59</t>
+          <t>-31,19; 13,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 7,88</t>
+          <t>-21,8; 9,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 14,38</t>
+          <t>-34,39; 18,5</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -3,9</t>
+          <t>-19,32; -3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 2,85</t>
+          <t>-16,29; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -4,37</t>
+          <t>-20,1; -4,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 3,37</t>
+          <t>-18,19; 3,15</t>
         </is>
       </c>
     </row>
